--- a/wooclap/imports/02_History_Part_2.xlsx
+++ b/wooclap/imports/02_History_Part_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$5</definedName>
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L00-C04 · A new technology is promised to solve almost every problem, but its first products often fail. What might happen next?</t>
+          <t>L00-C04 · A system performs well on a narrow benchmark. Its promoters claim that it is close to general intelligence, but deployments expose failures outside the benchmark. Which consequence could help produce an AI winter?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Funding must keep growing because the promises were ambitious.</t>
+          <t>Success on one benchmark proves broad intelligence, so expectations no longer matter.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Some people may lose confidence and reduce funding.</t>
+          <t>The gap between the claims and demonstrated capability may erode confidence and funding.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Every useful discovery made so far must be wrong.</t>
+          <t>Failures outside the benchmark show that no AI technique can ever work.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The technology must already work well in every setting.</t>
+          <t>Researchers must discard every useful result produced by the system.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,32 +560,32 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L00-C05 · What does the term “AI winter” describe?</t>
+          <t>L00-C05 · Which account best explains the two AI winters discussed in this lecture?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>A period when computers could not operate in cold weather.</t>
+          <t>One decisive paper proved that every AI approach was impossible.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>The date when all AI research permanently ended.</t>
+          <t>In each case, expectations met technical and economic limits; confidence and funding fell, but research continued.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>A period when every AI system became equally successful.</t>
+          <t>Hardware stopped improving, causing all AI research to end until the next boom.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>A period of reduced enthusiasm and funding for AI.</t>
+          <t>Both winters were planned pauses after AI systems had met their promises.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L00-C06 · You want a chatbot to answer in a particular format. Why might you include two example answers in your request?</t>
+          <t>L00-C06 · The same fixed language model receives two prompts. One gives only an instruction; the other also gives two input-output examples. The second follows the requested format more reliably. What is the best interpretation?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The examples guarantee that every fact in its answer will be correct.</t>
+          <t>The examples permanently updated the model’s weights for all future users.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The chatbot can use the examples only if you rewrite its software.</t>
+          <t>Following the format proves that every fact in the response is correct.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The examples show the pattern you want it to follow.</t>
+          <t>The examples changed the model’s context and guided this response; they did not by themselves retrain its weights.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Adding examples prevents the chatbot from reading the rest of the request.</t>
+          <t>The examples changed the model’s software, so future prompts no longer matter.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>L00-C07 · Name one idea or event from today’s AI history that you would explain to a friend. Explain it in one sentence.</t>
+          <t>L00-C07 · Choose two milestones from different eras in this lecture. In two sentences, explain how the later milestone addressed a limitation or opportunity left by the earlier one, and name one limitation that still remained.</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
